--- a/data/satisfaction_detail/2026/6月/散客.xlsx
+++ b/data/satisfaction_detail/2026/6月/散客.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>10</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>10</v>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>10</v>
@@ -536,8 +536,12 @@
           <t>园区停车方便</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -546,10 +550,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="9">
@@ -701,8 +705,12 @@
           <t>餐饮服务</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr"/>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -710,8 +718,12 @@
           <t>自助早餐</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr"/>
-      <c r="C21" s="4" t="inlineStr"/>
+      <c r="B21" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
